--- a/data/metadata/evidence_cases_v0.1.xlsx
+++ b/data/metadata/evidence_cases_v0.1.xlsx
@@ -1156,7 +1156,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>中高（公告明确；投产时间来自公司投资者关系记录转述，NEWS_007 链接待补）</t>
+          <t>中高（公告明确；投产时间来自公司投资者关系记录转述）</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>中高（2026 年节点高质量来源；2022 年投资额来自媒体转述，NEWS_013 链接待补）</t>
+          <t>中高（2026 年节点高质量来源；2022 年投资额来自媒体转述）</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">

--- a/data/metadata/evidence_cases_v0.1.xlsx
+++ b/data/metadata/evidence_cases_v0.1.xlsx
@@ -1768,7 +1768,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>凤凰科技（转路透社）</t>
+          <t>ANTARA（印尼国家通讯社）</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1779,7 +1779,7 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://tech.ifeng.com/c/8gLk1Msnjan</t>
+          <t>https://otomotif.antaranews.com/berita/5724273/pabrik-byd-di-subang-resmi-beroperasi-dan-serap-5000-pekerja-lokal</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>待核实原文</t>
+          <t>已核实（二手来源）</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1826,17 +1826,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>在西爪哇省苏邦工业园区建设印尼工厂，总投资约 10 亿美元，规划年产能 15 万辆，计划 2025 年底前竣工；与泰国工厂共同构成东南亚双基地，中国产能保留。</t>
+          <t>在西爪哇省苏邦 Smartpolitan 工业园区建设印尼工厂，投资约 16 万亿印尼盾（约 10 亿美元），最大年产能 15 万辆；2026-09-03 正式投产启用，为比亚迪全球第 13 座整车工厂。与泰国工厂共同构成东南亚双基地，中国产能保留。</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>待观察（建设中）</t>
+          <t>成功（已投产并转为全本地生产）</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>比亚迪 BYD：印尼是东南亚最大汽车市场，但整车进口关税高且要求本地化生产。 触发因素 tariff_pressure；最终 多地区混合布局。待观察（建设中）</t>
+          <t>比亚迪 BYD：印尼是东南亚最大汽车市场，但整车进口关税高且要求本地化生产。 触发因素 tariff_pressure；最终 多地区混合布局。成功（已投产并转为全本地生产）</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>中（来源为路透社转述的公司高管表态，竣工情况需以最新公告核实）</t>
+          <t>高（印尼国家通讯社 ANTARA 报道工厂投产、产能与停止整车进口）</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -2056,17 +2056,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>计划在越南北部（太原省）投资约 40 亿美元建设芯片测试与封装工厂，分阶段实施；中国西安等既有基地继续运营，形成'韩国 + 中国 + 越南'的多地产能结构。</t>
+          <t>计划在越南北部（太原省）投资约 15 亿美元建设芯片测试与封装工厂（已见报道的初始项目）。媒体另称可能追加约 25 亿美元的第二工厂投资——该项为条件性后续计划，尚未确认实施，不能与初始项目合并为单一'约 40 亿美元'已确定项目。中国西安等既有基地继续运营，形成'韩国 + 中国 + 越南'的多地产能结构。</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>待观察（计划阶段）</t>
+          <t>待观察（计划阶段；投资金额需拆分核实）</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>三星电子 Samsung Electronics：中美科技摩擦与关税使单一产地风险上升，越南被定位为分散地；同时 AI 需求推升存储芯片产能缺口。 触发因素 geopolitical_uncertainty；最终 多地区混合布局。待观察（计划阶段）</t>
+          <t>三星电子 Samsung Electronics：中美科技摩擦与关税使单一产地风险上升，越南被定位为分散地；同时 AI 需求推升存储芯片产能缺口。 触发因素 geopolitical_uncertainty；最终 多地区混合布局。待观察（计划阶段；投资金额需拆分核实）</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>中（多方媒体转述，未见公司正式公告）</t>
+          <t>中（媒体转述，未见公司正式公告；原新浪链接已失效，金额需以公司公告核实）</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>已核实（二手来源）</t>
+          <t>待核实原文</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
@@ -2286,17 +2286,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2025 年 7 月及 12 月，富士康两度从印度工厂撤回中国大陆工程师与技术团队，部分产能与订单回流中国大陆；印度的组装布局并未取消，但节奏明显放缓。</t>
+          <t>2025 年 7 月及 12 月，富士康两度要求/撤回其印度工厂的中国大陆工程师与技术团队（彭博社等报道）。印度的组装布局并未取消，但推进节奏明显放缓。注：现有证据仅支持'工程团队撤回、工程支持减弱'，不足以证明订单或产能已实际回流中国。</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>局部回流（未完全放弃印度）</t>
+          <t>工程团队撤回（订单/产能回流中国为待验证推断，未完全放弃印度）</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>富士康 Foxconn / 苹果 Apple（供应链）：为分散地缘风险，苹果推动印度组装比例提升，但印度工厂良率、配套与工程能力不足，关键组件仍依赖进口。 触发因素 geopolitical_uncertainty；最终 提高中国生产比例。局部回流（未完全放弃印度）</t>
+          <t>富士康 Foxconn / 苹果 Apple（供应链）：为分散地缘风险，苹果推动印度组装比例提升，但印度工厂良率、配套与工程能力不足，关键组件仍依赖进口。 触发因素 geopolitical_uncertainty；最终 提高中国生产比例。工程团队撤回（订单/产能回流中国为待验证推断，未完全放弃印度）</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>中高（多家媒体一致，均引自知情人士）</t>
+          <t>中（工程团队撤回有彭博社等报道支持；'订单/产能回流中国'缺乏直接证据，不可作为既定事实）</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -3445,17 +3445,17 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>待核实原文</t>
+          <t>已核实（二手来源）</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>凤凰科技（转路透社）</t>
+          <t>ANTARA（印尼国家通讯社）</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://tech.ifeng.com/c/8gLk1Msnjan</t>
+          <t>https://otomotif.antaranews.com/berita/5724273/pabrik-byd-di-subang-resmi-beroperasi-dan-serap-5000-pekerja-lokal</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>已核实（二手来源）</t>
+          <t>待核实原文</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
